--- a/Ministry_of_Foreign_Affairs.xlsx
+++ b/Ministry_of_Foreign_Affairs.xlsx
@@ -414,7 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E223"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
